--- a/02_Basic_Excel_for_Data_Analytics/10_Mini-project-Expense-Tracker.xlsx
+++ b/02_Basic_Excel_for_Data_Analytics/10_Mini-project-Expense-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01 COURSES\Learn_Data_Analytics_by_CWH\02_Basic_Excel_for_Data_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F345F136-2679-4AB2-A892-B305BB7EC20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D65AC3F-3600-48E8-B5A6-0436C88ED106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="622" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="13-December" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'12-December'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'12-December'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
